--- a/output/HS_Code_Summary_V-TOP_EUROPE_WPXA26B0826CZ501.xlsx
+++ b/output/HS_Code_Summary_V-TOP_EUROPE_WPXA26B0826CZ501.xlsx
@@ -44,7 +44,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -58,17 +58,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF6969"/>
+        <fgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
+        <fgColor rgb="FFFF6969"/>
       </patternFill>
     </fill>
     <fill>
@@ -133,21 +138,21 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -513,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -611,7 +616,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Části a součásti elektrických signalizačních přístrojů (EAS) – pevné samoobslužné schránky AM či RF (Double, Single, Triple Protection Box Wrap, Alarm Box) s magnetickým zámkem; pevné samoobslužné štítky s magnetickým kabelovým zámkem; štítky AM nebo RF s ocelovým nebo plastovým kabelem k ochraně lahví a plechovek; standardní tvrdé etikety (štítky) k ochraně textilu, oděvů a příslušenství – technologie RF / AM / RF &amp; AM a magnetický zámek. Určeno k ochraně zboží proti krádeži v obchodech.</t>
+          <t>Části a součásti elektrických signalizačních přístrojů (EAS) – pevné samoobslužné schránky AM či RF (Double, Single, Triple Protection Box Wrap, Alarm Box) s magnetickým zámkem; pevné samoobslužné štítky s magnetickým kabelovým zámkem; štítky AM nebo RF s ocelovým nebo plastovým kabelem k ochraně lahví a plechovek; standardní tvrdé etikety (štítky) k ochraně textilu, oděvů a příslušenství – technologie RF / AM / RF &amp; AM a magnetický zámek. Určeno k ochraně zboží proti krádeži v obchodech. Včetně vzorků štítků dodaných ve vzorkovém sáčku (položka SAMPLE BAG).</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -620,19 +625,19 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>259100</v>
+        <v>260100</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>4340.4</v>
+        <v>4350.9</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>4665</v>
+        <v>4676.1</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>4794.09</v>
+        <v>4805.5</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>38250.08</v>
+        <v>38270.08</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -641,11 +646,15 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>AS1038, AS1002E, AS1103E, AS1001E, BT3042, BT3055, HD2001, HD2030, HD2051, HD2085, HD2150, HD2045, HD2036, BT3018</t>
+          <t>AS1038, AS1002E, AS1103E, AS1001E, BT3042, BT3055, HD2001, HD2030, HD2051, HD2085, HD2150, HD2045, HD2036, BT3018, SAMPLE BAG</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Zahrnuje položku SAMPLE BAG (1 000 ks, 10,5 g/ks, 20,00 EUR) – na faktuře i packing listu bez kódu ONTIME. Zařazena k tomuto kódu na základě potvrzení klienta; hmotnost na kus odpovídá tvrdým štítkům řady HD.</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -702,7 +711,7 @@
           <t>HANGZHOU ONTIME I.T. CO., LTD., Hangzhou, CHINA</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>8205 59 80 00</t>
         </is>
@@ -742,12 +751,12 @@
           <t>DL4405 KEY, DT4002</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>POZOR – KÓD ZMĚNĚN</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="M4" s="6" t="inlineStr">
         <is>
           <t>V klíči byl u DL4405 KEY kód 7326 90 98 90 PŘEŠKRTNUT (neplatný) – použit platný kód 8205 59 80 00. Pozn.: 7326 je zboží CBAM, 8205 nikoli.</t>
         </is>
@@ -954,217 +963,160 @@
       <c r="M8" s="2" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>HANGZHOU ONTIME I.T. CO., LTD., Hangzhou, CHINA</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>NEZAŘAZENO</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE BAG (vzorkový sáček) – položka není uvedena v sazebníkovém klíči VTOP EUROPE (HS kódy 10.9.2026). HS kód nutno doplnit před podáním CP.</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>11.41</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>CFR Praha (CFR PRAGUE)</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>SAMPLE BAG</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="inlineStr">
-        <is>
-          <t>CHYBÍ HS KÓD</t>
-        </is>
-      </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>CHYBÍ HS KÓD – položka SAMPLE BAG není v sazebníkovém klíči. Nutno doplnit před podáním CP.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>CELKEM</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr"/>
-      <c r="C10" s="7" t="inlineStr"/>
-      <c r="D10" s="7" t="inlineStr"/>
-      <c r="E10" s="8" t="n">
+      <c r="B9" s="7" t="inlineStr"/>
+      <c r="C9" s="7" t="inlineStr"/>
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="8" t="n">
         <v>500554</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F9" s="9" t="n">
         <v>4536</v>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="G9" s="9" t="n">
         <v>4878</v>
       </c>
-      <c r="H10" s="9" t="n">
+      <c r="H9" s="9" t="n">
         <v>5013</v>
       </c>
-      <c r="I10" s="9" t="n">
+      <c r="I9" s="9" t="n">
         <v>43377.18</v>
       </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>CFR Praha</t>
         </is>
       </c>
-      <c r="K10" s="7" t="inlineStr"/>
-      <c r="L10" s="7" t="inlineStr"/>
-      <c r="M10" s="7" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="K9" s="7" t="inlineStr"/>
+      <c r="L9" s="7" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>LEGENDA A KONTROLNÍ SOUČTY</t>
         </is>
       </c>
     </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>🔵 MODRÁ</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Položka bez kódu ONTIME na faktuře – zařazena na základě potvrzení klienta, viz poznámka u kódu 8531 90 00 00.</t>
+        </is>
+      </c>
+    </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>🔴 ČERVENÁ</t>
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>🟠 ORANŽOVÁ</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Chybějící HS kód – nutno doplnit před podáním celního prohlášení.</t>
+          <t>HS kód v sazebníkovém klíči přeškrtnut / nahrazen – ověřeno a použit platný kód.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>🟠 ORANŽOVÁ</t>
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>Zásilka</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>HS kód v sazebníkovém klíči přeškrtnut / nahrazen – ověřeno a použit platný kód.</t>
+          <t>Odesílatel: HANGZHOU ONTIME I.T. CO., LTD., Hangzhou, Čína  |  Příjemce: V-TOP EUROPE s.r.o., Františka Diviše 1012/64, 104 00 Praha 22 Uhříněves, IČO 257 95 040, DIČ CZ25795040</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>Zásilka</t>
+          <t>Doklady</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Odesílatel: HANGZHOU ONTIME I.T. CO., LTD., Hangzhou, Čína  |  Příjemce: V-TOP EUROPE s.r.o., Františka Diviše 1012/64, 104 00 Praha 22 Uhříněves, IČO 257 95 040, DIČ CZ25795040</t>
+          <t>Faktura PI24200070026048B&amp;053&amp;054B ze dne 14.8.2026; Packing list k téže faktuře; potvrzení přepravy WPXA26B0826CZ501 (železniční přeprava Xi'an → Khorgos → Praha, odjezd 2.9.2026, 40HC NWRU8624306/003451032, CFS-CFS, freight prepaid).</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>Doklady</t>
+          <t>Incoterms</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>Faktura PI24200070026048B&amp;053&amp;054B ze dne 14.8.2026; Packing list k téže faktuře; potvrzení přepravy WPXA26B0826CZ501 (železniční přeprava Xi'an → Khorgos → Praha, odjezd 2.9.2026, 40HC NWRU8624306/003451032, CFS-CFS, freight prepaid).</t>
+          <t>CFR PRAGUE (CFR Praha) – uvedeno v poli TERMS obchodní faktury. Přepravné do Prahy je součástí fakturované ceny. Pozn.: CFR je doložka určená pro námořní/vnitrozemskou vodní přepravu, zde použita pro železniční přepravu – doporučeno ověřit s klientem (věcně odpovídá CPT Praha).</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>Incoterms</t>
+          <t>Množství</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>CFR PRAGUE (CFR Praha) – uvedeno v poli TERMS obchodní faktury. Přepravné do Prahy je součástí fakturované ceny. Pozn.: CFR je doložka určená pro námořní/vnitrozemskou vodní přepravu, zde použita pro železniční přepravu – doporučeno ověřit s klientem (věcně odpovídá CPT Praha).</t>
+          <t>500 554 ks – souhlasí s fakturou i packing listem.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>Množství</t>
+          <t>Hmotnosti</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>500 554 ks – souhlasí s fakturou i packing listem.</t>
+          <t>Čistá 4 536,00 kg; hrubá dle položek 4 878,00 kg; palety (9 ks) 135,00 kg; hrubá celkem 5 013,00 kg. Sloupec „Hrubá hmotnost vč. palet“ rozpouští tāru palet poměrně dle hrubé hmotnosti položek (faktor 1,027675).</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>Hmotnosti</t>
+          <t>Celní hodnota</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Čistá 4 536,00 kg; hrubá dle položek 4 878,00 kg; palety (9 ks) 135,00 kg; hrubá celkem 5 013,00 kg. Sloupec „Hrubá hmotnost vč. palet“ rozpouští tāru palet poměrně dle hrubé hmotnosti položek (faktor 1,027675).</t>
+          <t>43 377,18 EUR – souhlasí se součtem faktury (SUB TOTAL = TOTAL). Obchodní sleva nebyla na faktuře uplatněna, proporcionální rozpočet slevy se proto neprovádí.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>Celní hodnota</t>
+          <t>Sloučení</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>43 377,18 EUR – souhlasí se součtem faktury (SUB TOTAL = TOTAL). Obchodní sleva nebyla na faktuře uplatněna, proporcionální rozpočet slevy se proto neprovádí.</t>
+          <t>Řádky faktury sloučeny na unikátní HS kódy v rámci jednoho odesílatele (32 řádků faktury → 7 řádků). Zásilka má jediného odesílatele, proto nedochází ke kolizi stejného HS kódu napříč odesílateli.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>Sloučení</t>
+          <t>Zdroj popisů</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>Řádky faktury sloučeny na unikátní HS kódy v rámci jednoho odesílatele (32 řádků faktury → 8 řádků). Zásilka má jediného odesílatele, proto nedochází ke kolizi stejného HS kódu napříč odesílateli.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>Zdroj popisů</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>Sazebníkový klíč „VTOP EUROPE s.r.o. – HS kódy 10.9.2026.xlsx“, list List1. U kódů 3926 90 97 90 a 8205 59 80 00 použit „Návrh popisu do CP“. Text popisu u 3926 90 97 90 je ve zdrojovém souboru useknutý („…proti použit“) – doplněno na „proti neoprávněnému použití“, doporučeno potvrdit.</t>
         </is>
@@ -1173,8 +1125,8 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="C20:M20"/>
+    <mergeCell ref="C12:M12"/>
     <mergeCell ref="C21:M21"/>
-    <mergeCell ref="C22:M22"/>
     <mergeCell ref="C15:M15"/>
     <mergeCell ref="C16:M16"/>
     <mergeCell ref="C19:M19"/>
@@ -1501,22 +1453,22 @@
       <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>OTEVŘENÉ BODY K DOŘEŠENÍ</t>
         </is>
       </c>
-      <c r="B30" s="16" t="inlineStr"/>
+      <c r="B30" s="19" t="inlineStr"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="17" t="inlineStr">
         <is>
-          <t>1) SAMPLE BAG</t>
+          <t>1) SAMPLE BAG – VYŘEŠENO</t>
         </is>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>1 000 ks / 10,50 kg net / 20,00 EUR – chybí HS kód v sazebníkovém klíči. Nutno doplnit před podáním CP.</t>
+          <t>1 000 ks / 10,50 kg net / 20,00 EUR. Na faktuře ani na packing listu není uveden kód ONTIME a položka není v sazebníkovém klíči. Po potvrzení klientem zařazena pod 8531 90 00 00 (vzorky štítků) a sloučena do tohoto řádku. Podpůrný argument: 10,50 kg / 1 000 ks = 10,5 g na kus, což odpovídá tvrdým štítkům řady HD (HD2051 = 10,9 g/ks), nikoli prázdným plastovým sáčkům (jinak 3923 21 00 00).</t>
         </is>
       </c>
     </row>
